--- a/artfynd/A 7717-2024 artfynd.xlsx
+++ b/artfynd/A 7717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,6 +950,306 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115109312</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79527</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Småfloarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504466</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7007384</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på en gammal lutande sälg där det även växer desto mer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115108768</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79528</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Småfloarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504466</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7007384</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om skrovellav på en gammal lutande sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7717-2024 artfynd.xlsx
+++ b/artfynd/A 7717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2861,6 +2861,284 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120596706</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småfloarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504385</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7007333</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en smal sälg. Vid observationstillfället var bålarna uttorkade. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Talldominerad skog med inslag av gran, björk och sälg på frisk- och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120596193</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Småfloarna, Frusmyrmyrarna, Lit, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504546</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7007227</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observation av två talltitor som var mycket aktiva på fyndplatsen. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre barrdominerad, luckig och flerskiktad skog med gran, tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7717-2024 artfynd.xlsx
+++ b/artfynd/A 7717-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115109529</v>
+        <v>115108768</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Garnlav på gran i måttliga mängder. Här växer garnlav även på tall. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Gott om skrovellav på en gammal lutande sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +782,27 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,15 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115108768</v>
+        <v>115633296</v>
       </c>
       <c r="B3" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,11 +850,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504466</v>
+        <v>504554</v>
       </c>
       <c r="R3" t="n">
-        <v>7007383</v>
+        <v>7007241</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en gammal lutande sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Måttlig påväxt av skrovellav på sälg. Här växer även lunglav och stuplav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Grov bark på sälgens nedre del av stammen. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -961,46 +961,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115109312</v>
+        <v>115109529</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1048,7 +1039,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav på en gammal lutande sälg där det även växer desto mer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Garnlav på gran i måttliga mängder. Här växer garnlav även på tall. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,27 +1064,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1114,16 +1095,11 @@
         <v>115109837</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1252,19 +1228,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115631788</v>
+        <v>115631552</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1295,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504498</v>
+        <v>504437</v>
       </c>
       <c r="R6" t="n">
-        <v>7007289</v>
+        <v>7007290</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1335,7 +1306,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Hyfsat långväxta bålar av garnlav på gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1393,46 +1364,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115633980</v>
+        <v>115631788</v>
       </c>
       <c r="B7" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1440,10 +1402,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504554</v>
+        <v>504498</v>
       </c>
       <c r="R7" t="n">
-        <v>7007233</v>
+        <v>7007289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1480,7 +1442,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Måttlig påväxt av stuplav på sälg. Här växer även lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Enstaka långväxta bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1500,32 +1462,27 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1543,46 +1500,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115633849</v>
+        <v>115632027</v>
       </c>
       <c r="B8" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1590,13 +1538,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504554</v>
+        <v>504516</v>
       </c>
       <c r="R8" t="n">
-        <v>7007233</v>
+        <v>7007262</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1630,7 +1578,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bitvis riklig påväxt av lunglav på sälg. Här växer även lunglav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Relativt gott om garnlav med många långväxta bålar på flera träd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1655,27 +1603,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
+          <t>På mer än 12 st granar inom ca 10 meters radie. Finns här även på björk.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
+          <t>Branch on living tree # Picea abies # På mer än 12 st granar inom ca 10 meters radie. Finns här även på björk.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1693,19 +1641,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115635780</v>
+        <v>115632454</v>
       </c>
       <c r="B9" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1728,11 +1671,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1740,10 +1679,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504378</v>
+        <v>504545</v>
       </c>
       <c r="R9" t="n">
-        <v>7007216</v>
+        <v>7007250</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1780,7 +1719,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Relativt ymnig påväxt av garnlav på flertalet granar. Några av lavbålarna har apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1800,7 +1739,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre grandominerad och luckig skog med inslag av tall och björk på blöt och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1813,11 +1752,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Garnlav på minst 6 st. granar.</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1825,7 +1759,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Garnlav på minst 6 st. granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1843,46 +1777,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115632726</v>
+        <v>115635569</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1890,10 +1815,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504554</v>
+        <v>504522</v>
       </c>
       <c r="R10" t="n">
-        <v>7007241</v>
+        <v>7007219</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1930,7 +1855,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fläckvis påväxt av lunglav på sälg med bitvis grova soralrika bålar. Här växer även skrovellav och stuplav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,32 +1875,32 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>Garnlav på minst 7 st. granar inom ca 10 meters radie.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>Branch on living tree # Picea abies # Garnlav på minst 7 st. granar inom ca 10 meters radie.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1993,42 +1918,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115633296</v>
+        <v>115635780</v>
       </c>
       <c r="B11" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2036,10 +1960,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504554</v>
+        <v>504378</v>
       </c>
       <c r="R11" t="n">
-        <v>7007241</v>
+        <v>7007216</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2076,7 +2000,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Måttlig påväxt av skrovellav på sälg. Här växer även lunglav och stuplav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Relativt ymnig påväxt av garnlav på flertalet granar. Några av lavbålarna har apothecier. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2096,32 +2020,32 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Äldre grandominerad och luckig skog med inslag av tall och björk på blöt och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>Garnlav på minst 6 st. granar.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark på sälgens nedre del av stammen. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>Branch on living tree # Picea abies # Garnlav på minst 6 st. granar.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2139,15 +2063,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115632027</v>
+        <v>115109312</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2155,26 +2074,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2182,13 +2105,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504516</v>
+        <v>504466</v>
       </c>
       <c r="R12" t="n">
-        <v>7007262</v>
+        <v>7007383</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2222,7 +2145,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Relativt gott om garnlav med många långväxta bålar på flera träd. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Lunglav på en gammal lutande sälg där det även växer desto mer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2242,32 +2165,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk och sälg på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>På mer än 12 st granar inom ca 10 meters radie. Finns här även på björk.</t>
+          <t>En levande gammal lutande sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # På mer än 12 st granar inom ca 10 meters radie. Finns här även på björk.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En levande gammal lutande sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2285,15 +2208,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115631552</v>
+        <v>115632726</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2301,26 +2219,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2328,10 +2250,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504437</v>
+        <v>504554</v>
       </c>
       <c r="R13" t="n">
-        <v>7007290</v>
+        <v>7007241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2368,7 +2290,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hyfsat långväxta bålar av garnlav på gran.</t>
+          <t>Fläckvis påväxt av lunglav på sälg med bitvis grova soralrika bålar. Här växer även skrovellav och stuplav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2388,27 +2310,32 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre grandominerad och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk och frisk-fuktig mark.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2426,44 +2353,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115633498</v>
+        <v>115633849</v>
       </c>
       <c r="B14" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2476,7 +2398,7 @@
         <v>504554</v>
       </c>
       <c r="R14" t="n">
-        <v>7007241</v>
+        <v>7007233</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2513,7 +2435,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Måttlig påväxt av stuplav på sälg. Här växer även lunglav och skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Bitvis riklig påväxt av lunglav på sälg. Här växer även lunglav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2548,7 +2470,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2558,7 +2480,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark på sälgens nedre del av stammen. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2576,15 +2498,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115632454</v>
+        <v>120596706</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2592,26 +2509,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2619,10 +2540,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504545</v>
+        <v>504385</v>
       </c>
       <c r="R15" t="n">
-        <v>7007250</v>
+        <v>7007333</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2649,17 +2570,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Enstaka bålar av lunglav på en smal sälg. Vid observationstillfället var bålarna uttorkade. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2674,32 +2595,32 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Talldominerad skog med inslag av gran, björk och sälg på frisk- och frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2717,42 +2638,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115635569</v>
+        <v>115633498</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2760,10 +2680,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504522</v>
+        <v>504554</v>
       </c>
       <c r="R16" t="n">
-        <v>7007219</v>
+        <v>7007241</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2800,7 +2720,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Måttlig påväxt av stuplav på sälg. Här växer även lunglav och skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2820,32 +2740,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Garnlav på minst 7 st. granar inom ca 10 meters radie.</t>
+          <t>En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Garnlav på minst 7 st. granar inom ca 10 meters radie.</t>
+          <t>Bark on living woody plant # Grov bark på sälgens nedre del av stammen. # Salix caprea # En tvåstammig sälg med brösthöjdsdiameter på 31 cm. Sälgen är delvis skadad och angripen av vedsvamp.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2863,69 +2783,55 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120596193</v>
+        <v>115633980</v>
       </c>
       <c r="B17" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Småfloarna, Frusmyrmyrarna, Lit, Jmt</t>
+          <t>Småfloarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504546</v>
+        <v>504554</v>
       </c>
       <c r="R17" t="n">
-        <v>7007227</v>
+        <v>7007233</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2949,17 +2855,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Observation av två talltitor som var mycket aktiva på fyndplatsen. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Måttlig påväxt av stuplav på sälg. Här växer även lunglav. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2968,17 +2874,43 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrdominerad, luckig och flerskiktad skog med gran, tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+          <t>Äldre grandominerad, luckig och flerskiktad skog med inslag av tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En trestammig sälg där den grövsta stammen har en brösthöjdsdiameter på 39 cm.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2996,15 +2928,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120596706</v>
+        <v>120596193</v>
       </c>
       <c r="B18" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3012,44 +2939,53 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Småfloarna, Jmt</t>
+          <t>Småfloarna, Frusmyrmyrarna, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504385</v>
+        <v>504546</v>
       </c>
       <c r="R18" t="n">
-        <v>7007333</v>
+        <v>7007227</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3083,7 +3019,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en smal sälg. Vid observationstillfället var bålarna uttorkade. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
+          <t>Observation av två talltitor som var mycket aktiva på fyndplatsen. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 7717-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3092,38 +3028,17 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Talldominerad skog med inslag av gran, björk och sälg på frisk- och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Äldre barrdominerad, luckig och flerskiktad skog med gran, tall, björk, sälg och gråal på frisk-fuktig till fuktig mark.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 7717-2024 artfynd.xlsx
+++ b/artfynd/A 7717-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115108768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -958,6 +968,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115633296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115109529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1225,6 +1245,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115109837</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1361,6 +1386,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115631552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1497,6 +1527,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115631788</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1638,6 +1673,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632027</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1774,6 +1814,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1915,6 +1960,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115635569</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2060,6 +2110,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115635780</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2205,6 +2260,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115109312</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2350,6 +2410,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632726</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2495,6 +2560,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115633849</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2635,6 +2705,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596706</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2780,6 +2855,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115633498</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2925,6 +3005,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115633980</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3053,8 +3138,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120596193</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>